--- a/下定商品匯入模板-境外.xlsx
+++ b/下定商品匯入模板-境外.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+  <si>
+    <t>類型</t>
+  </si>
   <si>
     <t>SKU</t>
   </si>
@@ -25,6 +28,9 @@
     <t>數量</t>
   </si>
   <si>
+    <t>一般下定商品</t>
+  </si>
+  <si>
     <t>所有欄位皆為必填</t>
   </si>
   <si>
@@ -35,7 +41,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -45,6 +51,11 @@
     <font>
       <color theme="1"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -67,12 +78,15 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
@@ -293,31 +307,38 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="6" width="12.63"/>
+    <col customWidth="1" min="1" max="1" width="18.38"/>
+    <col customWidth="1" min="2" max="7" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="G2" s="3" t="s">
-        <v>4</v>
+      <c r="A2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="G3" s="3" t="s">
-        <v>5</v>
+      <c r="H3" s="4" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1"/>
@@ -1318,6 +1339,11 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
+  <dataValidations>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="A2">
+      <formula1>"一般下定商品,贈品"</formula1>
+    </dataValidation>
+  </dataValidations>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>